--- a/Sindhi Muslim/Classes/GBPS Data for Software.xlsx
+++ b/Sindhi Muslim/Classes/GBPS Data for Software.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9499BE-FAE9-402F-BFE8-A1C5771A2409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0031DC60-27D6-4426-9BA9-A947D4D339BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2754,11 +2754,11 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3368,22 +3368,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
     </row>
     <row r="2" spans="1:14" s="11" customFormat="1" ht="15.75">
       <c r="A2" s="8" t="s">
@@ -5843,7 +5843,7 @@
       <c r="M60" s="32" t="s">
         <v>600</v>
       </c>
-      <c r="N60" s="56" t="s">
+      <c r="N60" s="55" t="s">
         <v>57</v>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       <c r="M64" s="32" t="s">
         <v>604</v>
       </c>
-      <c r="N64" s="56" t="s">
+      <c r="N64" s="55" t="s">
         <v>57</v>
       </c>
     </row>
@@ -9627,7 +9627,7 @@
       <c r="M151" s="53" t="s">
         <v>685</v>
       </c>
-      <c r="N151" s="56" t="s">
+      <c r="N151" s="55" t="s">
         <v>57</v>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       <c r="L180" s="38" t="s">
         <v>644</v>
       </c>
-      <c r="M180" s="57" t="s">
+      <c r="M180" s="56" t="s">
         <v>786</v>
       </c>
       <c r="N180" s="38" t="s">
@@ -10904,7 +10904,7 @@
       <c r="L181" s="38" t="s">
         <v>726</v>
       </c>
-      <c r="M181" s="57" t="s">
+      <c r="M181" s="56" t="s">
         <v>606</v>
       </c>
       <c r="N181" s="38" t="s">
@@ -10955,91 +10955,91 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:14" ht="15.75">
-      <c r="A183" s="16">
-        <v>19</v>
-      </c>
-      <c r="B183" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C183" s="18">
+    <row r="183" spans="1:14" s="50" customFormat="1" ht="15.75">
+      <c r="A183" s="32">
+        <v>19</v>
+      </c>
+      <c r="B183" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C183" s="37">
         <v>658</v>
       </c>
-      <c r="D183" s="14" t="s">
+      <c r="D183" s="40" t="s">
         <v>406</v>
       </c>
-      <c r="E183" s="15" t="s">
+      <c r="E183" s="35" t="s">
         <v>222</v>
       </c>
-      <c r="F183" s="16" t="s">
+      <c r="F183" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="G183" s="16" t="s">
+      <c r="G183" s="32" t="s">
         <v>392</v>
       </c>
-      <c r="H183" s="20">
+      <c r="H183" s="49">
         <v>42651</v>
       </c>
-      <c r="I183" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J183" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K183" s="20">
+      <c r="I183" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="J183" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="K183" s="49">
         <v>45140</v>
       </c>
-      <c r="L183" s="7" t="s">
+      <c r="L183" s="38" t="s">
         <v>702</v>
       </c>
-      <c r="M183" s="31" t="s">
+      <c r="M183" s="56" t="s">
         <v>621</v>
       </c>
-      <c r="N183" s="7" t="s">
+      <c r="N183" s="38" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:14" ht="15.75">
-      <c r="A184" s="16">
-        <v>20</v>
-      </c>
-      <c r="B184" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C184" s="18">
+    <row r="184" spans="1:14" s="50" customFormat="1" ht="15.75">
+      <c r="A184" s="32">
+        <v>20</v>
+      </c>
+      <c r="B184" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C184" s="37">
         <v>785</v>
       </c>
-      <c r="D184" s="14" t="s">
+      <c r="D184" s="40" t="s">
         <v>379</v>
       </c>
-      <c r="E184" s="15" t="s">
+      <c r="E184" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="F184" s="16" t="s">
+      <c r="F184" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="G184" s="16" t="s">
+      <c r="G184" s="32" t="s">
         <v>392</v>
       </c>
-      <c r="H184" s="20">
+      <c r="H184" s="49">
         <v>42685</v>
       </c>
-      <c r="I184" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J184" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K184" s="20">
+      <c r="I184" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="J184" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="K184" s="49">
         <v>45303</v>
       </c>
-      <c r="L184" s="7" t="s">
+      <c r="L184" s="38" t="s">
         <v>727</v>
       </c>
-      <c r="M184" s="28" t="s">
+      <c r="M184" s="54" t="s">
         <v>728</v>
       </c>
-      <c r="N184" s="7" t="s">
+      <c r="N184" s="38" t="s">
         <v>57</v>
       </c>
     </row>
